--- a/(s395172) Dharma_Bahadur_Budhathoki/Individual Timesheets - Dharma Bahadur budhathoki(S395172).xlsx
+++ b/(s395172) Dharma_Bahadur_Budhathoki/Individual Timesheets - Dharma Bahadur budhathoki(S395172).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\clz\oraEarn\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\clz\oraEarn\(s395172) Dharma_Bahadur_Budhathoki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA7DA348-E3A9-4DAA-A1E4-897EAD008D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5E26A5-492D-4EB4-B8E4-47FC10459886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A9310762-FDEB-4380-9087-495A89237B89}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{A9310762-FDEB-4380-9087-495A89237B89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="19">
   <si>
     <t>Week</t>
   </si>
@@ -78,6 +78,24 @@
   </si>
   <si>
     <t>Finalised the OraEarn project concept, including the Aura AI advisor, earnings-to-expenses-to-savings flow, savings goals, analytics dashboard, notifications, and target users.</t>
+  </si>
+  <si>
+    <t>Week 05</t>
+  </si>
+  <si>
+    <t>Contributed as Scrum Master by coordinating with team members on GitHub branching, pulling the latest changes from main, resolving merge conflicts correctly, and agreeing on a review process before merging changes.</t>
+  </si>
+  <si>
+    <t>Participated in the class discussion of the OraEarn ERD and applied database normalisation principles to identify and reduce data redundancy and improve data integrity.</t>
+  </si>
+  <si>
+    <t>Reviewed the required OraEarn features and translated the final requirements into technical requirements for the application as the main Developer.</t>
+  </si>
+  <si>
+    <t>Started the OraEarn application development by setting up the backend and frontend project structure, configuring the development environment, and preparing the application for further implementation.</t>
+  </si>
+  <si>
+    <t>Set up the initial database context and required development packages, then configured and edited the database models and attributes according to the final ERD.</t>
   </si>
 </sst>
 </file>
@@ -462,10 +480,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04423912-C767-489D-B66D-2127194B2034}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -499,7 +517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -516,7 +534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -533,7 +551,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -550,7 +568,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -567,47 +585,107 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/(s395172) Dharma_Bahadur_Budhathoki/Individual Timesheets - Dharma Bahadur budhathoki(S395172).xlsx
+++ b/(s395172) Dharma_Bahadur_Budhathoki/Individual Timesheets - Dharma Bahadur budhathoki(S395172).xlsx
@@ -1,130 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\clz\oraEarn\(s395172) Dharma_Bahadur_Budhathoki\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5E26A5-492D-4EB4-B8E4-47FC10459886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{A9310762-FDEB-4380-9087-495A89237B89}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="19">
-  <si>
-    <t>Week</t>
-  </si>
-  <si>
-    <t>StudentId</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Hours [1-6]</t>
-  </si>
-  <si>
-    <t>Activity details</t>
-  </si>
-  <si>
-    <t>S395172</t>
-  </si>
-  <si>
-    <t>Week 04</t>
-  </si>
-  <si>
-    <t>Dharma Bahadur Budhathoki</t>
-  </si>
-  <si>
-    <t>Defined the core functionality of OraEarn, including job and hourly-rate management, shift tracking, automatic pay calculation, expense tracking, savings goals, and financial analytics.</t>
-  </si>
-  <si>
-    <t>Identified OraEarn as the most suitable project concept for helping hourly workers manage earnings, expenses, and savings in one platform.</t>
-  </si>
-  <si>
-    <t>Analysed existing alternatives and competitors for shift tracking, budgeting, and Developed the initial project canvas for OraEarn, focusing on target user.</t>
-  </si>
-  <si>
-    <t>Discussed student visa work-hour monitoring and designed the concept for alerts to help users manage their permitted working hour</t>
-  </si>
-  <si>
-    <t>Finalised the OraEarn project concept, including the Aura AI advisor, earnings-to-expenses-to-savings flow, savings goals, analytics dashboard, notifications, and target users.</t>
-  </si>
-  <si>
-    <t>Week 05</t>
-  </si>
-  <si>
-    <t>Contributed as Scrum Master by coordinating with team members on GitHub branching, pulling the latest changes from main, resolving merge conflicts correctly, and agreeing on a review process before merging changes.</t>
-  </si>
-  <si>
-    <t>Participated in the class discussion of the OraEarn ERD and applied database normalisation principles to identify and reduce data redundancy and improve data integrity.</t>
-  </si>
-  <si>
-    <t>Reviewed the required OraEarn features and translated the final requirements into technical requirements for the application as the main Developer.</t>
-  </si>
-  <si>
-    <t>Started the OraEarn application development by setting up the backend and frontend project structure, configuring the development environment, and preparing the application for further implementation.</t>
-  </si>
-  <si>
-    <t>Set up the initial database context and required development packages, then configured and edited the database models and attributes according to the final ERD.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -143,23 +57,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -479,212 +452,431 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04423912-C767-489D-B66D-2127194B2034}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>StudentId</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Hours [1-6]</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Activity details</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Week 04</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Identified OraEarn as the most suitable project concept for helping hourly workers manage earnings, expenses, and savings in one platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Week 04</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Analysed existing alternatives and competitors for shift tracking, budgeting, and Developed the initial project canvas for OraEarn, focusing on target user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Week 04</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Defined the core functionality of OraEarn, including job and hourly-rate management, shift tracking, automatic pay calculation, expense tracking, savings goals, and financial analytics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Week 04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Discussed student visa work-hour monitoring and designed the concept for alerts to help users manage their permitted working hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Week 04</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Finalised the OraEarn project concept, including the Aura AI advisor, earnings-to-expenses-to-savings flow, savings goals, analytics dashboard, notifications, and target users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Week 05</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Reviewed the required OraEarn features and translated the final requirements into technical requirements for the application as the main Developer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Week 05</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Contributed as Scrum Master by coordinating with team members on GitHub branching, pulling the latest changes from main, resolving merge conflicts correctly, and agreeing on a review process before merging changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Week 05</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Participated in the class discussion of the OraEarn ERD and applied database normalisation principles to identify and reduce data redundancy and improve data integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Week 05</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Started the OraEarn application development by setting up the backend and frontend project structure, configuring the development environment, and preparing the application for further implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Week 05</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Set up the initial database context and required development packages, then configured and edited the database models and attributes according to the final ERD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Week 06</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Researched how to connect the OraEarn application to the database, including the required packages, connection configuration, and Entity Framework setup for PostgreSQL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Week 06</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Completed the frontend and backend project setup using the required packages and configured the development environment for further implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Week 06</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>18</v>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Developed the frontend and backend according to the final ERD and finalised the database schema, models, and attributes to match the normalised design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Week 06</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Started the Aura AI chat feature with the backend as the main focus; the frontend chat interface still needs to be refined.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Week 06</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Attended the individual meeting to review Week 6 progress, the database and application setup, and the remaining frontend work.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/(s395172) Dharma_Bahadur_Budhathoki/Individual Timesheets - Dharma Bahadur budhathoki(S395172).xlsx
+++ b/(s395172) Dharma_Bahadur_Budhathoki/Individual Timesheets - Dharma Bahadur budhathoki(S395172).xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -754,6 +754,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -876,6 +877,132 @@
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Attended the individual meeting to review Week 6 progress, the database and application setup, and the remaining frontend work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Week 07</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Developed application authentication, including registration, login, JWT tokens, and protected access for users and admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Week 07</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Built the admin dashboard so pending registrations can be reviewed, approved, or rejected, and admin-only pages stay restricted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Week 07</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Implemented expense CRUD (create, read, update, and delete) using REST APIs in ASP.NET Core, including expense records and related category data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Week 07</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Used REST with .NET and Swagger while building these features, to test and document the auth, admin, and expense endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Week 07</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>S395172</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Dharma Bahadur Budhathoki</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Attended the individual meeting to review Week 7 authentication, admin dashboard, and expense CRUD, and to plan Week 8 Swagger and AI chatbot work.</t>
         </is>
       </c>
     </row>
